--- a/output/recog_y/recog_y_result.xlsx
+++ b/output/recog_y/recog_y_result.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="recogY地址" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="楼层房间展开" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="结果" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="明细" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="查询计划" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="查询汇总" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'查询计划'!$A$1:$G$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'查询汇总'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'明细'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'查询计划'!$A$1:$L$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'查询汇总'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,25 +438,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,72 +460,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>查询关键词</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>候选总数</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>recogFlag分布</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>匹配地址</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>buildingCode</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ofcaCode</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>clientType</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>运营商</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>楼层数</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>房间数</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>房间号</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>明细状态</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>离线筛查</t>
+          <t>Flat</t>
         </is>
       </c>
     </row>
@@ -551,16 +480,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -576,31 +512,1493 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>查询关键词</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>匹配地址</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>buildingCode</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>房间号</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>组合来源</t>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>楼层数</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>房间数</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>组合总数</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>实际探测次数</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recogFlag分布</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>离线筛查</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>馬鞍山翠擁華庭第9座</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>馬鞍山翠擁華庭第9座</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>F006;C001;C004;A005;D001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>馬鞍山翠擁華庭第9座</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>馬鞍山翠擁華庭第9座</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>F006;C001;C004;A005;D001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>沙田大圍美城苑貴城閣</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>沙田大圍美城苑貴城閣</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>F006;C001;C004;A005</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>沙田第一城第一座</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>沙田第一城第一座</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>F006;C001;C004;A005</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>康寧間,康寧道,觀塘,九龍</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>康寧間,康寧道,觀塘,九龍</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>A002;C005;D001</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>康寧間,康寧道,觀塘,九龍</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>康寧間,康寧道,觀塘,九龍</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>A002;C005;D001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>康寧間,康寧道,觀塘,九龍</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>康寧間,康寧道,觀塘,九龍</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>A002;C005;D001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>愉澤閣</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>愉澤閣</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>C001;C002;C004;C005;A005;D003;A006</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>愉澤閣,愉田苑,銀城街,沙田,新界</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>愉澤閣,愉田苑,銀城街,沙田,新界</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>愉澤閣,愉田苑,銀城街,沙田,新界</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>愉澤閣,愉田苑,銀城街,沙田,新界</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>愉和閣</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>愉和閣</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>C001;C002;C004;C005;A005;A006</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>愉悅閣</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>愉悅閣</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>C001;C002;C004;C005;A005;A006</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>愉健閣</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>愉健閣</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>C001;C002;C004;C005;A005;A006</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>愉群閣</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>愉群閣</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>C001;C002;C004;C005;A005;A006</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>愉逸閣</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>愉逸閣</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>C001;C002;C004;C005;A005;A006</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>愉瑞閣</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>愉瑞閣</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>C001;C002;C004;C005;A005;A006</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>慶盛閣，穗禾苑，穗禾路，沙田，新界</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>慶盛閣，穗禾苑，穗禾路，沙田，新界</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>F001;D001</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>慶盛閣，穗禾苑，穗禾路，沙田，新界</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>慶盛閣，穗禾苑，穗禾路，沙田，新界</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>F001;D001</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>第1座,名城1期,美田路,大圍,沙田,新界</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>第1座,名城1期,美田路,大圍,沙田,新界</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>无问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>第2座,名城1期,美田路,大圍,沙田,新界</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>第2座,名城1期,美田路,大圍,沙田,新界</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>无问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>第3座,名城1期,美田路,大圍,沙田,新界</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>第3座,名城1期,美田路,大圍,沙田,新界</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>无问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>第5座,名城1期,美田路,大圍,沙田,新界</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>第5座,名城1期,美田路,大圍,沙田,新界</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>无问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">華園樓,竹園南邨,竹園道,竹園,九龍 </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>華園樓,竹園南邨,竹園道,竹園,九龍</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>F002</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>藍田鯉安苑鯉景閣e座</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>藍田鯉安苑鯉景閣e座</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>F003;F006;C001;C004;A005</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>日出康城XIIB期 2B座</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>日出康城XIIB期 2B座</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>F006;F007;C001;C002;C004;A005</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>定志閣,兆安苑,屯興路,屯門,新界</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>定志閣,兆安苑,屯興路,屯門,新界</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>无问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>第七座,順利紀律部隊宿舍,利安道,牛頭角,九龍樓層</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>第七座,順利紀律部隊宿舍,利安道,牛頭角,九龍樓層</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B座,觀龍樓第2期,龍華街,堅尼地城,港島</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B座,觀龍樓第2期,龍華街,堅尼地城,港島</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>无问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>第三十座,華翠園,穗禾路,沙田,新界</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>第三十座,華翠園,穗禾路,沙田,新界</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>第十七座,珀麗灣,珀麗路,馬灣,新界</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>第十七座,珀麗灣,珀麗路,馬灣,新界</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>无问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>啟悅閣,啟翔苑,彩虹道,新蒲崗,九龍</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>啟悅閣,啟翔苑,彩虹道,新蒲崗,九龍</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>无问题</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -611,16 +2009,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -641,20 +2044,45 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>候选总数</t>
+          <t>匹配地址</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>buildingCode</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>楼层数</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>房间数</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>组合总数</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>实际探测次数</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>recogFlag分布</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>未命中原因</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>离线筛查</t>
         </is>
@@ -674,18 +2102,33 @@
           <t>馬鞍山翠擁華庭第9座</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>F006;C001;C004;A005</t>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>F006;C001;C004;A005;D001</t>
         </is>
       </c>
     </row>
@@ -703,18 +2146,33 @@
           <t>馬鞍山翠擁華庭第9座</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>F006;C001;C004;A005</t>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>F006;C001;C004;A005;D001</t>
         </is>
       </c>
     </row>
@@ -732,16 +2190,31 @@
           <t>沙田大圍美城苑貴城閣</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>F006;C001;C004;A005</t>
         </is>
@@ -761,16 +2234,31 @@
           <t>沙田第一城第一座</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>F006;C001;C004;A005</t>
         </is>
@@ -790,18 +2278,33 @@
           <t>康寧間,康寧道,觀塘,九龍</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>A002;C005</t>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>A002;C005;D001</t>
         </is>
       </c>
     </row>
@@ -819,18 +2322,33 @@
           <t>康寧間,康寧道,觀塘,九龍</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>A002;C005</t>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>A002;C005;D001</t>
         </is>
       </c>
     </row>
@@ -848,18 +2366,33 @@
           <t>康寧間,康寧道,觀塘,九龍</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>A002;C005</t>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>A002;C005;D001</t>
         </is>
       </c>
     </row>
@@ -877,18 +2410,33 @@
           <t>愉澤閣</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>C001;C002;C004;C005;A005</t>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>C001;C002;C004;C005;A005;D003;A006</t>
         </is>
       </c>
     </row>
@@ -906,18 +2454,33 @@
           <t>愉澤閣,愉田苑,銀城街,沙田,新界</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>无问题</t>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>D001</t>
         </is>
       </c>
     </row>
@@ -935,18 +2498,33 @@
           <t>愉澤閣,愉田苑,銀城街,沙田,新界</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>无问题</t>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>D001</t>
         </is>
       </c>
     </row>
@@ -964,18 +2542,33 @@
           <t>愉和閣</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>C001;C002;C004;C005;A005</t>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>C001;C002;C004;C005;A005;A006</t>
         </is>
       </c>
     </row>
@@ -993,18 +2586,33 @@
           <t>愉悅閣</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>C001;C002;C004;C005;A005</t>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>C001;C002;C004;C005;A005;A006</t>
         </is>
       </c>
     </row>
@@ -1022,18 +2630,33 @@
           <t>愉健閣</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>C001;C002;C004;C005;A005</t>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>C001;C002;C004;C005;A005;A006</t>
         </is>
       </c>
     </row>
@@ -1051,18 +2674,33 @@
           <t>愉群閣</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>C001;C002;C004;C005;A005</t>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>C001;C002;C004;C005;A005;A006</t>
         </is>
       </c>
     </row>
@@ -1080,18 +2718,33 @@
           <t>愉逸閣</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>C001;C002;C004;C005;A005</t>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>C001;C002;C004;C005;A005;A006</t>
         </is>
       </c>
     </row>
@@ -1109,18 +2762,33 @@
           <t>愉瑞閣</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>C001;C002;C004;C005;A005</t>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>C001;C002;C004;C005;A005;A006</t>
         </is>
       </c>
     </row>
@@ -1138,18 +2806,33 @@
           <t>慶盛閣，穗禾苑，穗禾路，沙田，新界</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>F001</t>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>F001;D001</t>
         </is>
       </c>
     </row>
@@ -1167,18 +2850,33 @@
           <t>慶盛閣，穗禾苑，穗禾路，沙田，新界</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>F001</t>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>F001;D001</t>
         </is>
       </c>
     </row>
@@ -1196,16 +2894,31 @@
           <t>第1座,名城1期,美田路,大圍,沙田,新界</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>无问题</t>
         </is>
@@ -1225,16 +2938,31 @@
           <t>第2座,名城1期,美田路,大圍,沙田,新界</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>无问题</t>
         </is>
@@ -1254,16 +2982,31 @@
           <t>第3座,名城1期,美田路,大圍,沙田,新界</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>无问题</t>
         </is>
@@ -1283,16 +3026,31 @@
           <t>第5座,名城1期,美田路,大圍,沙田,新界</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>无问题</t>
         </is>
@@ -1312,16 +3070,31 @@
           <t>華園樓,竹園南邨,竹園道,竹園,九龍</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>F002</t>
         </is>
@@ -1341,16 +3114,31 @@
           <t>藍田鯉安苑鯉景閣e座</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>F003;F006;C001;C004;A005</t>
         </is>
@@ -1370,16 +3158,31 @@
           <t>日出康城XIIB期 2B座</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>F006;F007;C001;C002;C004;A005</t>
         </is>
@@ -1399,16 +3202,31 @@
           <t>定志閣,兆安苑,屯興路,屯門,新界</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>无问题</t>
         </is>
@@ -1428,16 +3246,31 @@
           <t>第七座,順利紀律部隊宿舍,利安道,牛頭角,九龍樓層</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>A001</t>
         </is>
@@ -1457,16 +3290,31 @@
           <t>B座,觀龍樓第2期,龍華街,堅尼地城,港島</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>无问题</t>
         </is>
@@ -1486,16 +3334,31 @@
           <t>第三十座,華翠園,穗禾路,沙田,新界</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>A003</t>
         </is>
@@ -1515,16 +3378,31 @@
           <t>第十七座,珀麗灣,珀麗路,馬灣,新界</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>无问题</t>
         </is>
@@ -1544,23 +3422,38 @@
           <t>啟悅閣,啟翔苑,彩虹道,新蒲崗,九龍</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>未调用接口(plan 模式只生成查询计划)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>未查询(接口未调用或运行中止)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>无问题</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G32"/>
+  <autoFilter ref="A1:L32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1571,7 +3464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1653,19 +3546,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>recogFlag=Y 候选总条数</t>
+          <t>未命中(bad case)数</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>未查询, 不适用</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>楼层×房间组合数</t>
+          <t>getInstallInfo 探测总次数</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1677,29 +3570,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>未命中(bad case)数</t>
+          <t>调用失败数</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>未查询, 不适用</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>调用失败数</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
           <t>0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>